--- a/secondary_genes/fisher_int_secondary_genes.xlsx
+++ b/secondary_genes/fisher_int_secondary_genes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anqiwang/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anqiwang/Documents/GitHub/Ozone-and-Lung-Functions/secondary_genes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD7C6F7-DC17-0243-BB32-401AC4E7159A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{335898CD-6ED3-2D42-909B-49B561BF9E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="900" windowWidth="27240" windowHeight="15940" xr2:uid="{52971CBB-3A60-F24A-94D3-8EF76DBA44C7}"/>
+    <workbookView xWindow="4840" yWindow="1780" windowWidth="27240" windowHeight="15940" xr2:uid="{52971CBB-3A60-F24A-94D3-8EF76DBA44C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>CpG</t>
   </si>
@@ -65,10 +65,16 @@
     <t>C6orf227</t>
   </si>
   <si>
-    <t>fisher CI lower</t>
-  </si>
-  <si>
     <t>fisher CI upper</t>
+  </si>
+  <si>
+    <t>fisher int lower</t>
+  </si>
+  <si>
+    <t>CI lower</t>
+  </si>
+  <si>
+    <t>CI upper</t>
   </si>
 </sst>
 </file>
@@ -451,14 +457,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22D2C70-0559-6940-A98C-4AC1FE48DFD1}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="15.1640625" customWidth="1"/>
     <col min="4" max="4" width="14.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -466,13 +472,19 @@
         <v>6</v>
       </c>
       <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" t="s">
-        <v>10</v>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -485,8 +497,14 @@
       <c r="D2">
         <v>1.342105E-2</v>
       </c>
+      <c r="E2">
+        <v>4.4191170630274402E-3</v>
+      </c>
+      <c r="F2">
+        <v>1.34012735780061E-2</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -499,8 +517,14 @@
       <c r="D3">
         <v>2.6152359999999999E-2</v>
       </c>
+      <c r="E3">
+        <v>9.43697326840311E-3</v>
+      </c>
+      <c r="F3">
+        <v>2.6137560727357401E-2</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -513,8 +537,14 @@
       <c r="D4">
         <v>9.2770079999999998E-3</v>
       </c>
+      <c r="E4">
+        <v>2.9067204374384199E-3</v>
+      </c>
+      <c r="F4">
+        <v>9.2714508210968195E-3</v>
+      </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -527,8 +557,14 @@
       <c r="D5">
         <v>3.2868420000000002E-2</v>
       </c>
+      <c r="E5">
+        <v>7.8913915412638994E-3</v>
+      </c>
+      <c r="F5">
+        <v>3.2782174466970702E-2</v>
+      </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -540,6 +576,12 @@
       </c>
       <c r="D6">
         <v>4.4903039999999998E-2</v>
+      </c>
+      <c r="E6">
+        <v>1.20735127094516E-2</v>
+      </c>
+      <c r="F6">
+        <v>4.4794309510645898E-2</v>
       </c>
     </row>
   </sheetData>

--- a/secondary_genes/fisher_int_secondary_genes.xlsx
+++ b/secondary_genes/fisher_int_secondary_genes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anqiwang/Documents/GitHub/Ozone-and-Lung-Functions/secondary_genes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{335898CD-6ED3-2D42-909B-49B561BF9E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7882AB25-F433-4849-8B35-9A807F8E38B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4840" yWindow="1780" windowWidth="27240" windowHeight="15940" xr2:uid="{52971CBB-3A60-F24A-94D3-8EF76DBA44C7}"/>
+    <workbookView xWindow="12840" yWindow="620" windowWidth="28800" windowHeight="16360" xr2:uid="{52971CBB-3A60-F24A-94D3-8EF76DBA44C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>CpG</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>CI upper</t>
+  </si>
+  <si>
+    <t>mean_diff</t>
   </si>
 </sst>
 </file>
@@ -457,14 +460,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22D2C70-0559-6940-A98C-4AC1FE48DFD1}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="15.1640625" customWidth="1"/>
     <col min="4" max="4" width="14.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -483,8 +486,11 @@
       <c r="F1" t="s">
         <v>12</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -503,8 +509,11 @@
       <c r="F2">
         <v>1.34012735780061E-2</v>
       </c>
+      <c r="G2">
+        <v>8.9101953205167894E-3</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -523,8 +532,11 @@
       <c r="F3">
         <v>2.6137560727357401E-2</v>
       </c>
+      <c r="G3">
+        <v>1.7787266997880219E-2</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -543,8 +555,11 @@
       <c r="F4">
         <v>9.2714508210968195E-3</v>
       </c>
+      <c r="G4">
+        <v>6.0890856292676217E-3</v>
+      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -563,8 +578,11 @@
       <c r="F5">
         <v>3.2782174466970702E-2</v>
       </c>
+      <c r="G5">
+        <v>2.033678300411729E-2</v>
+      </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -582,6 +600,9 @@
       </c>
       <c r="F6">
         <v>4.4794309510645898E-2</v>
+      </c>
+      <c r="G6">
+        <v>2.843391111004873E-2</v>
       </c>
     </row>
   </sheetData>
